--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4301075268817204</v>
+        <v>0.4623655913978494</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4366197183098591</v>
+        <v>0.4436619718309859</v>
       </c>
       <c r="D2">
-        <v>0.6666666666666666</v>
+        <v>0.6475409836065574</v>
       </c>
       <c r="E2">
         <v>93</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
